--- a/subspaces/04-academic-tutoring/specialized-major-tutor-agent/agent/QA.xlsx
+++ b/subspaces/04-academic-tutoring/specialized-major-tutor-agent/agent/QA.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,44 +413,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Answer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Sub_Topic</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Source_Reference</t>
+          <t>Display as Suggested Question?
+yes/no</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Phân biệt sự khác nhau giữa Regularization L1 (Lasso) và L2 (Ridge) trong hồi quy tuyến tính.</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -462,25 +450,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Phân biệt sự khác nhau giữa Regularization L1 (Lasso) và L2 (Ridge) trong hồi quy tuyến tính.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>L1 thêm số hạng phạt bằng tổng trị tuyệt đối các trọng số (lambda * sum|w|). Do có góc nhọn tại các trục tọa độ, L1 có xu hướng ép các trọng số không quan trọng về đúng bằng 0, giúp chọn lọc đặc trưng (Feature Selection) và tạo ra mô hình thưa (Sparse Model). L2 thêm số hạng phạt bằng tổng bình phương trọng số (lambda * sum(w^2)), kéo các trọng số về gần 0 nhưng hiếm khi bằng 0 hoàn toàn, giúp khắc phục hiện tượng đa cộng tuyến (Multicollinearity) và hạn chế Overfitting.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hàm mất mát Cross-Entropy trong bài toán phân loại nhị phân được tính theo công thức nào?</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -492,25 +467,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hàm mất mát Cross-Entropy trong bài toán phân loại nhị phân được tính theo công thức nào?</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Công thức hàm mất mát nhị phân (Binary Cross-Entropy Loss): L(y, y_hat) = - [y * log(y_hat) + (1 - y) * log(1 - y_hat)], trong đó y thuộc {0, 1} là nhãn thực tế của mẫu và y_hat = sigmoid(z) thuộc (0, 1) là xác suất dự đoán lớp dương của mô hình. Khi dự đoán hoàn toàn tự tin và chính xác, loss = 0; khi dự đoán sai lệch hoàn toàn, loss tiến ra vô cùng.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nguyên lý hoạt động của thuật toán K-Means và cách khởi tạo tâm cụm bằng K-Means++.</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -519,28 +481,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nguyên lý hoạt động của thuật toán K-Means và cách khởi tạo tâm cụm bằng K-Means++.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K-Means luân phiên giữa 2 bước: 1) Gán mỗi điểm dữ liệu vào tâm cụm gần nhất (dựa trên khoảng cách Euclidean). 2) Cập nhật lại vị trí tâm cụm bằng trung bình tọa độ của các điểm thuộc cụm đó. Để tránh rơi vào nghiệm cục bộ xấu do khởi tạo ngẫu nhiên, K-Means++ chọn tâm cụm đầu tiên ngẫu nhiên, sau đó các tâm cụm tiếp theo được chọn theo phân phối xác suất tỉ lệ thuận với bình phương khoảng cách ngắn nhất D(x)^2 đến các tâm cụm đã có, giúp các tâm cụm ban đầu phân bố cách xa nhau nhất có thể.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chỉ số Precision, Recall và F1-score đánh giá mô hình trong trường hợp mất cân bằng dữ liệu như thế nào?</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -551,30 +500,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Chỉ số Precision, Recall và F1-score đánh giá mô hình trong trường hợp mất cân bằng dữ liệu như thế nào?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- Precision = TP / (TP + FP): Đo lường trong số các mẫu được dự đoán là Dương tính thì có bao nhiêu mẫu đúng thực tế (ưu tiên khi cần tránh báo động giả, ví dụ lọc spam email).
-- Recall = TP / (TP + FN): Đo lường mô hình bắt được bao nhiêu phần trăm số mẫu Dương tính thực tế (ưu tiên khi không được phép bỏ sót, ví dụ chẩn đoán bệnh ung thư, phát hiện gian lận).
-- F1-Score = 2 * (Precision * Recall) / (Precision + Recall): Trung bình điều hòa giữa Precision và Recall, phản ánh chính xác hiệu năng khi dữ liệu mất cân bằng nghiêm trọng.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hiện tượng Overfitting (Quá khớp) và Underfitting (Dưới khớp): Dấu hiệu nhận biết và cách khắc phục.</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -587,26 +521,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Hiện tượng Overfitting (Quá khớp) và Underfitting (Dưới khớp): Dấu hiệu nhận biết và cách khắc phục.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>- Overfitting: Mô hình có Training Loss rất thấp nhưng Validation/Test Loss lại cao (High Variance). Khắc phục: Bổ sung thêm dữ liệu huấn luyện, áp dụng Regularization (L1/L2/Dropout), giảm độ phức tạp mô hình, Early Stopping.
-- Underfitting: Mô hình có cả Training Loss và Validation Loss đều cao (High Bias). Khắc phục: Tăng độ phức tạp của mô hình (tăng số tầng/số nơ-ron), kỹ thuật tạo đặc trưng mới (Feature Engineering), giảm hệ số phạt Regularization.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Giải thuật Hỗ trợ Vector (SVM) tìm siêu phẳng phân tách tối ưu dựa trên nguyên lý nào?</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -618,25 +538,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Giải thuật Hỗ trợ Vector (SVM) tìm siêu phẳng phân tách tối ưu dựa trên nguyên lý nào?</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SVM tìm siêu phẳng phân tách có lề (Margin - khoảng cách từ siêu phẳng đến các điểm dữ liệu gần nhất của mỗi lớp gọi là Support Vectors) đạt giá trị LỚN NHẤT. Với dữ liệu không phân tách tuyến tính được, SVM sử dụng hàm hạt nhân (Kernel Trick: RBF, Polynomial, Sigmoid) để ánh xạ ngầm định không gian dữ liệu đầu vào lên một không gian nhiều chiều hơn, nơi dữ liệu trở nên phân tách tuyến tính.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Khái niệm Gradient Descent (GD), Stochastic Gradient Descent (SGD) và Mini-batch GD.</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -650,27 +557,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Khái niệm Gradient Descent (GD), Stochastic Gradient Descent (SGD) và Mini-batch GD.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>- Batch GD: Dùng TOÀN BỘ tập dữ liệu để tính đạo hàm gradient tại mỗi bước lặp; cập nhật chính xác nhưng cực kỳ chậm và tốn RAM với dữ liệu lớn.
-- SGD: Chỉ dùng DUY NHẤT 1 mẫu ngẫu nhiên cho mỗi lần cập nhật; tính toán siêu nhanh nhưng quỹ đạo cập nhật dao động mạnh (noisy).
-- Mini-batch GD: Thỏa hiệp tối ưu, chia dữ liệu thành các lô nhỏ (batch size 32, 64, 128) để cập nhật; tận dụng khả năng tính toán song song của GPU và hội tụ ổn định.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Thuật toán Random Forest kết hợp các Cây quyết định bằng kỹ thuật gì?</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -682,25 +574,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Thuật toán Random Forest kết hợp các Cây quyết định bằng kỹ thuật gì?</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Random Forest sử dụng kỹ thuật Bagging (Bootstrap Aggregating): Tạo nhiều tập dữ liệu con bằng cách lấy mẫu có hoàn lại từ tập dữ liệu gốc, huấn luyện độc lập các Cây quyết định (Decision Tree) trên từng tập con đó. Đồng thời, tại mỗi nút phân nhánh, chỉ một tập con ngẫu nhiên các đặc trưng được xem xét. Kết quả cuối cùng được lấy theo biểu quyết đa số (Majority Voting) cho phân loại hoặc trung bình cộng cho hồi quy, giúp giảm mạnh hiện tượng Overfitting của từng cây đơn lẻ.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mô hình Naive Bayes dựa trên giả định ngây thơ nào?</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -712,25 +591,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Mô hình Naive Bayes dựa trên giả định ngây thơ nào?</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Naive Bayes dựa trên Định lý xác suất Bayes: P(y|X) = [P(y) * P(X|y)] / P(X). Giả định 'ngây thơ' (naive) cốt lõi là: TẤT CẢ các đặc trưng x_1, x_2,..., x_n hoàn toàn ĐỘC LẬP có điều kiện với nhau khi biết trước nhãn lớp y: P(X|y) = P(x1|y) * P(x2|y) * ... * P(xn|y). Mặc dù giả định này hiếm khi đúng trong thực tế, Naive Bayes vẫn hoạt động đặc biệt hiệu quả trong bài toán phân loại văn bản và lọc thư rác.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kỹ thuật Giảm số chiều PCA (Principal Component Analysis) hoạt động như thế nào?</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -742,25 +608,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Kỹ thuật Giảm số chiều PCA (Principal Component Analysis) hoạt động như thế nào?</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PCA là phương pháp học không giám sát giúp giảm số chiều của dữ liệu trong khi vẫn giữ lại phương sai lớn nhất có thể. Các bước: 1) Chuẩn hóa dữ liệu về trung bình 0. 2) Tính ma trận hiệp phương sai. 3) Tìm các trị riêng (Eigenvalues) và vector riêng (Eigenvectors) của ma trận hiệp phương sai. 4) Chiếu dữ liệu ban đầu lên các vector riêng tương ứng với các trị riêng lớn nhất (các thành phần chính - Principal Components).</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ma trận nhầm lẫn (Confusion Matrix) gồm các đại lượng nào?</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -772,25 +625,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ma trận nhầm lẫn (Confusion Matrix) gồm các đại lượng nào?</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Gồm bảng 2x2 cho phân loại nhị phân: TP (True Positive: Dự đoán Đúng mẫu Dương), TN (True Negative: Dự đoán Đúng mẫu Âm), FP (False Positive: Sai lầm loại 1 - Âm tính nhưng dự đoán là Dương tính), FN (False Negative: Sai lầm loại 2 - Dương tính nhưng dự đoán là Âm tính). Từ 4 đại lượng này tính ra Accuracy = (TP + TN) / (TP + TN + FP + FN), Precision, Recall và Specificity.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Đường cong ROC và chỉ số AUC (Area Under the Curve) có ý nghĩa gì?</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -802,25 +642,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Đường cong ROC và chỉ số AUC (Area Under the Curve) có ý nghĩa gì?</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Đường cong ROC biểu diễn mối quan hệ giữa Tỷ lệ dương tính thật (TPR = Recall) trên trục tung và Tỷ lệ dương tính giả (FPR = 1 - Specificity) trên trục hoành khi thay đổi ngưỡng phân loại (threshold) từ 0 đến 1. AUC là diện tích dưới đường cong ROC (nằm từ 0.5 đến 1.0). AUC càng gần 1.0 chứng tỏ mô hình phân tách giữa hai lớp càng hoàn hảo; AUC = 0.5 tương đương với việc đoán ngẫu nhiên.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Toán tử Sobel phát hiện biên theo phương ngang và phương dọc bằng các ma trận kernel nào?</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -832,31 +659,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Toán tử Sobel phát hiện biên theo phương ngang và phương dọc bằng các ma trận kernel nào?</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Toán tử Sobel sử dụng hai ma trận nhân chập 3x3 để xấp xỉ đạo hàm bậc nhất theo phương ngang Gx và phương dọc Gy:
-- Gx = [[-1, 0, 1], [-2, 0, 2], [-1, 0, 1]]
-- Gy = [[-1, -2, -1], [0, 0, 0], [1, 2, 1]]
-Độ lớn gradient biên tại mỗi điểm ảnh được tính: G = sqrt(Gx^2 + Gy^2) hoặc xấp xỉ G = |Gx| + |Gy|. Hướng của biên: theta = arctan(Gy / Gx).</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trình bày 4 bước cốt lõi của thuật toán dò biên Canny (Canny Edge Detector).</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -868,31 +679,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Trình bày 4 bước cốt lõi của thuật toán dò biên Canny (Canny Edge Detector).</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1. Khử nhiễu ảnh: Sử dụng bộ lọc Gaussian 5x5 để làm mịn ảnh và loại bỏ nhiễu.
-2. Tính gradient cường độ: Dùng toán tử Sobel để tính độ lớn và hướng của gradient biên tại mỗi pixel.
-3. Nén cực đại cục bộ (Non-Maximum Suppression): Giữ lại các điểm có độ lớn gradient đạt cực đại cục bộ theo hướng gradient, làm mảnh đường biên chỉ còn 1 pixel.
-4. Phân ngưỡng kép và nối biên (Hysteresis Thresholding): Sử dụng hai ngưỡng T_high và T_low; điểm &gt; T_high là biên chắc chắn, điểm &lt; T_low bị loại; điểm nằm giữa chỉ được giữ lại nếu có nối với một biên chắc chắn.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nguyên lý nén ảnh JPEG dựa trên phép biến đổi nào?</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -904,25 +699,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nguyên lý nén ảnh JPEG dựa trên phép biến đổi nào?</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>JPEG chia ảnh thành các khối 8x8 pixel, chuyển đổi từ miền không gian sang miền tần số bằng phép biến đổi Cosine rời rạc (Discrete Cosine Transform - DCT). Phép biến đổi DCT tập trung phần lớn năng lượng hình ảnh vào các hệ số tần số thấp (góc trên bên trái). Sau đó, bảng lượng tử hóa (Quantization) loại bỏ triệt để các hệ số tần số cao (mắt người ít nhạy cảm), rồi quét theo đường zic-zắc và nén dữ liệu bằng mã hóa Huffman/RLE.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cân bằng lược đồ xám (Histogram Equalization) có tác dụng gì đối với ảnh thiếu sáng?</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -934,25 +716,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Cân bằng lược đồ xám (Histogram Equalization) có tác dụng gì đối với ảnh thiếu sáng?</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Histogram Equalization dàn đều phân bố mật độ mức xám của ảnh trên toàn bộ dải động từ 0 đến 255. Phương pháp này biến đổi lược đồ mức xám ban đầu thông qua hàm phân phối tích lũy xác suất (Cumulative Distribution Function - CDF), giúp tăng độ tương phản tổng thể của ảnh một cách tự động, làm nổi rõ các chi tiết bị chìm trong vùng quá tối hoặc quá sáng.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bộ lọc Trung vị (Median Filter) có ưu thế gì vượt trội so với Bộ lọc Trung bình (Mean Filter)?</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -964,25 +733,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bộ lọc Trung vị (Median Filter) có ưu thế gì vượt trội so với Bộ lọc Trung bình (Mean Filter)?</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bộ lọc Trung vị là bộ lọc phi tuyến: Nó thay thế giá trị pixel trung tâm bằng giá trị trung vị của các pixel trong cửa sổ lân cận. Ưu thế vượt trội: Khử cực kỳ hiệu quả nhiễu muối tiêu (Salt-and-Pepper Noise / Impulse Noise) và ĐẶC BIỆT KHÔNG LÀM MỜ CÁC ĐƯỜNG BIÊN (Edge-preserving), trong khi bộ lọc trung bình tuyến tính làm mờ nhòe toàn bộ biên ảnh.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Phép toán hình thái học Giãn (Dilation) và Co (Erosion) trên ảnh nhị phân hoạt động ra sao?</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -995,26 +751,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Phép toán hình thái học Giãn (Dilation) và Co (Erosion) trên ảnh nhị phân hoạt động ra sao?</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>- Co (Erosion): Phần tử cấu trúc B trượt trên ảnh A; pixel trung tâm chỉ được giữ lại (giá trị 1) nếu TOÀN BỘ phần tử B nằm lọt hoàn toàn trong đối tượng A. Tác dụng: Làm mảnh đối tượng, loại bỏ các đốm nhiễu nhỏ.
-- Giãn (Dilation): Pixel trung tâm nhận giá trị 1 nếu có ÍT NHẤT MỘT điểm của phần tử B chạm vào đối tượng A. Tác dụng: Lấp đầy các lỗ thủng nhỏ, nối liền các đoạn đứt gãy.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phép Mở (Opening) và Phép Đóng (Closing) trong hình thái học được tạo thành như thế nào?</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1027,26 +769,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Phép Mở (Opening) và Phép Đóng (Closing) trong hình thái học được tạo thành như thế nào?</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>- Phép Mở: Thực hiện phép Co (Erosion) trước, sau đó Giãn (Dilation) bằng cùng phần tử cấu trúc. Tác dụng: Loại bỏ nhiễu trắng nhỏ bên ngoài đối tượng mà không làm thay đổi kích thước tổng thể.
-- Phép Đóng: Thực hiện Giãn (Dilation) trước, sau đó Co (Erosion). Tác dụng: Bịt kín các khe nứt, lấp đầy các khoảng trống tối nhỏ bên trong đối tượng.</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thuật toán phân ngưỡng Otsu tự động tìm ngưỡng nhị phân hóa ảnh tối ưu dựa trên tiêu chí nào?</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1058,25 +786,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Thuật toán phân ngưỡng Otsu tự động tìm ngưỡng nhị phân hóa ảnh tối ưu dựa trên tiêu chí nào?</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Thuật toán Otsu duyệt qua tất cả các mức xám t khả dĩ (0 đến 255) và chọn giá trị t sao cho Phương sai giữa hai lớp (Between-class variance: sigma_B^2) đạt giá trị LỚN NHẤT (tương đương với việc Cực tiểu hóa phương sai nội lớp). Phương pháp này hoàn toàn tự động, tối ưu tuyệt đối cho ảnh có lược đồ xám 2 đỉnh (Bimodal Histogram).</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Không gian màu HSV khác biệt với không gian màu RGB ở điểm cốt lõi nào?</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1088,25 +803,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Không gian màu HSV khác biệt với không gian màu RGB ở điểm cốt lõi nào?</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RGB là không gian màu dựa trên sự pha trộn vật lý của 3 kênh màu cơ bản (Red, Green, Blue), nhược điểm là thông tin màu sắc và cường độ ánh sáng bị hòa trộn vào nhau. HSV phân tách trực quan theo cảm nhận thị giác con người: Hue (Sắc độ màu: góc từ 0 đến 360 độ), Saturation (Độ bão hòa/độ thuần khiết của màu) và Value (Độ sáng). HSV rất thuận tiện cho các bài toán phân đoạn và nhận diện vật thể theo màu sắc bất chấp sự thay đổi của ánh sáng môi trường.</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bộ lọc Laplace (Laplacian) phát hiện biên bằng đạo hàm bậc hai gặp nhược điểm gì và giải pháp LoG?</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1118,25 +820,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bộ lọc Laplace (Laplacian) phát hiện biên bằng đạo hàm bậc hai gặp nhược điểm gì và giải pháp LoG?</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Toán tử Laplace dùng đạo hàm bậc hai để tìm biên qua các điểm chuyển qua mức không (Zero-crossing). Nhược điểm: Cực kỳ nhạy cảm với nhiễu ảnh (nhiễu bị khuếch đại mạnh ở đạo hàm bậc hai). Giải pháp: Bộ lọc Laplacian of Gaussian (LoG) kết hợp làm mịn ảnh bằng bộ lọc Gauss trước, sau đó mới áp dụng đạo hàm Laplace, giúp phát hiện biên chính xác và kháng nhiễu hiệu quả.</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cấu trúc mạng Feistel trong chuẩn mã hóa khối DES hoạt động ra sao?</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1145,28 +834,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Cấu trúc mạng Feistel trong chuẩn mã hóa khối DES hoạt động ra sao?</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Mạng Feistel chia khối dữ liệu 64-bit thành 2 nửa bằng nhau: Trái L_i-1 và Phải R_i-1. Tại mỗi vòng (trong tổng số 16 vòng): R_i = L_i-1 XOR F(R_i-1, K_i) và L_i = R_i-1. Điểm ưu việt tuyệt đối của mạng Feistel là: Quá trình Giải mã có cấu trúc phần cứng GIỐNG HỆT quá trình Mã hóa, chỉ cần đưa các khóa con K_i vào theo thứ tự ngược lại (từ K_16 về K_1).</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thuật toán mã hóa khóa công khai RSA: Trình bày quy trình sinh khóa, mã hóa và giải mã.</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1177,30 +853,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Thuật toán mã hóa khóa công khai RSA: Trình bày quy trình sinh khóa, mã hóa và giải mã.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1. Sinh khóa: Chọn 2 số nguyên tố lớn ngẫu nhiên p, q. Tính n = p*q và phi(n) = (p-1)*(q-1). Chọn số e sao cho 1 &lt; e &lt; phi(n) và gcd(e, phi(n)) = 1. Tính khóa bí mật d sao cho d * e ≡ 1 (mod phi(n)) bằng thuật toán Euclide mở rộng. Khóa công khai là (e, n), khóa riêng là (d, n).
-2. Mã hóa thông điệp M: C = M^e mod n.
-3. Giải mã bản mã C: M = C^d mod n.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Hàm băm mật mã (Cryptographic Hash Function) bắt buộc phải thỏa mãn 3 tính chất an toàn nào?</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1211,30 +872,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Hàm băm mật mã (Cryptographic Hash Function) bắt buộc phải thỏa mãn 3 tính chất an toàn nào?</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1. Kháng tiền ảnh (Preimage Resistance / One-way): Cho trước giá trị băm h, bất khả thi về mặt tính toán để tìm ra thông điệp m sao cho Hash(m) = h.
-2. Kháng tiền ảnh thứ hai (Second Preimage Resistance / Weak Collision): Cho trước thông điệp m1, bất khả thi để tìm thông điệp m2 != m1 sao cho Hash(m1) = Hash(m2).
-3. Kháng va chạm (Collision Resistance / Strong Collision): Bất khả thi để tìm ra BẤT KỲ cặp thông điệp m1 != m2 nào thỏa Hash(m1) = Hash(m2).</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tấn công ngày sinh (Birthday Attack) đe dọa độ an toàn của hàm băm như thế nào?</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1246,25 +892,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Tấn công ngày sinh (Birthday Attack) đe dọa độ an toàn của hàm băm như thế nào?</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Dựa trên Nghịch lý ngày sinh (Birthday Paradox): Xác suất tìm thấy 2 người có cùng ngày sinh trong phòng 23 người đạt &gt; 50%. Tương tự, với một hàm băm sinh mã n-bit (có 2^n giá trị khả dĩ), kẻ tấn công chỉ cần thử ngẫu nhiên khoảng 2^(n/2) thông điệp là đã có xác suất &gt; 50% tìm thấy va chạm (Collision). Do đó, hàm băm MD5 (128-bit) chỉ có độ an toàn va chạm là 2^64 (đã bị phá vỡ hoàn toàn), và hiện nay phải dùng tối thiểu SHA-256 (độ an toàn 2^128).</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Giao thức trao đổi khóa Diffie-Hellman hoạt động dựa trên bài toán toán học khó nào?</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1276,25 +909,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Giao thức trao đổi khóa Diffie-Hellman hoạt động dựa trên bài toán toán học khó nào?</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Diffie-Hellman dựa trên độ khó của bài toán Logarit rời rạc (Discrete Logarithm Problem) trên trường hữu hạn: Cho số nguyên tố lớn p và phần tử sinh g; nếu biết a, dễ dàng tính A = g^a mod p; nhưng nếu chỉ biết A, g và p thì bất khả thi để tìm lại số mũ bí mật a. Hai bên Alice và Bob trao đổi công khai A và B, sau đó cùng tính được khóa bí mật chung K = B^a mod p = A^b mod p = g^(a*b) mod p.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Phân biệt hai chế độ hoạt động của mã hóa khối: ECB (Electronic Codebook) và CBC (Cipher Block Chaining).</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1304,29 +924,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Phân biệt hai chế độ hoạt động của mã hóa khối: ECB (Electronic Codebook) và CBC (Cipher Block Chaining).</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>- ECB: Mỗi khối bản rõ được mã hóa hoàn toàn độc lập với cùng một khóa K. Nhược điểm chí mạng: Các khối bản rõ giống nhau sẽ sinh ra các khối bản mã GIỐNG HỆT NHAU, làm lộ cấu trúc và hình ảnh của dữ liệu (vụ rò rỉ hình chim cánh cụt Linux ECB kinh điển).
-- CBC: Khối bản rõ hiện tại được XOR với khối bản mã trước đó rồi mới đưa vào hàm mã hóa (khối đầu tiên XOR với vector khởi tạo IV ngẫu nhiên). Các khối bản mã phụ thuộc dây chuyền vào nhau, triệt tiêu hoàn toàn tính lặp mẫu của ECB.</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chữ ký số (Digital Signature) đảm bảo những thuộc tính an toàn thông tin nào?</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1338,25 +944,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Chữ ký số (Digital Signature) đảm bảo những thuộc tính an toàn thông tin nào?</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Đảm bảo 3 thuộc tính: 1. Toàn vẹn (Integrity): Thông điệp không bị chỉnh sửa lén lút (bảo vệ bởi hàm băm). 2. Xác thực nguồn gốc (Authentication): Người nhận chắc chắn bức thư gửi từ đúng người sở hữu khóa riêng tương ứng. 3. Không thể chối bỏ (Non-repudiation): Người ký không thể phủ nhận việc mình đã ký thông điệp đó vì chỉ duy nhất họ sở hữu khóa riêng bí mật (Private Key).</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hệ mã hóa chuẩn nâng cao AES (Advanced Encryption Standard) gồm những phép biến đổi nào trong mỗi vòng?</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1368,25 +961,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Hệ mã hóa chuẩn nâng cao AES (Advanced Encryption Standard) gồm những phép biến đổi nào trong mỗi vòng?</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mỗi vòng chuẩn của AES-128 (10 vòng) thực hiện 4 phép biến đổi trên ma trận trạng thái State 4x4 byte: 1. SubBytes: Thay thế phi tuyến từng byte độc lập qua bảng S-box. 2. ShiftRows: Dịch vòng các hàng byte sang trái (hàng 0 dịch 0, hàng 1 dịch 1, hàng 2 dịch 2, hàng 3 dịch 3). 3. MixColumns: Nhân chập các cột trong trường Galois GF(2^8) để khuếch tán dữ liệu (vòng cuối bỏ qua bước này). 4. AddRoundKey: XOR ma trận State với khóa con của vòng.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tấn công trung gian (Man-in-the-Middle - MitM) vào giao thức Diffie-Hellman cổ điển được khắc phục ra sao?</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1398,25 +978,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Tấn công trung gian (Man-in-the-Middle - MitM) vào giao thức Diffie-Hellman cổ điển được khắc phục ra sao?</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Diffie-Hellman cổ điển không có cơ chế xác thực danh tính (Authentication), kẻ tấn công đứng giữa có thể đánh tráo khóa công khai A và B để thiết lập 2 kênh mã hóa riêng rẽ với Alice và Bob. Khắc phục: Kết hợp Chữ ký số hoặc Chứng chỉ số X.509 (như trong giao thức TLS/SSL) để xác thực khóa công khai của mỗi bên trước khi tính khóa phiên chung.</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Mật mã đường cong Elliptic (ECC) có ưu thế gì vượt trội so với RSA?</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1428,25 +995,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Mật mã đường cong Elliptic (ECC) có ưu thế gì vượt trội so với RSA?</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ECC dựa trên bài toán logarit rời rạc trên nhóm các điểm của đường cong Elliptic. Ưu thế vượt trội: Cung cấp cùng cấp độ an toàn mật mã nhưng với ĐỘ DÀI KHÓA NGẮN HƠN RẤT NHIỀU so với RSA. Ví dụ: Khóa ECC 256-bit có độ an toàn tương đương khóa RSA 3072-bit. Nhờ đó, ECC tốn ít bộ nhớ hơn, tiêu thụ ít năng lượng hơn và tốc độ tính toán nhanh hơn, đặc biệt lý tưởng cho thiết bị di động và IoT.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Phân biệt hai mẫu thiết kế Factory Method và Abstract Factory. Cho ví dụ thực tế.</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1456,29 +1010,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Phân biệt hai mẫu thiết kế Factory Method và Abstract Factory. Cho ví dụ thực tế.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>- Factory Method: Dùng một phương thức ảo (thường trong cùng lớp Creator) để giao việc khởi tạo một đối tượng sản phẩm cụ thể cho lớp con quyết định (ví dụ: Dialog có phương thức createButton() trả về WindowsButton hoặc MacButton).
-- Abstract Factory: Là một interface cấp cao định nghĩa các phương thức để tạo ra cả một HỌ CÁC ĐỐI TƯỢNG có liên quan mật thiết với nhau (ví dụ: GUIFactory có createButton(), createCheckbox() -&gt; WindowsFactory tạo (WindowsButton, WindowsCheckbox), MacFactory tạo (MacButton, MacCheckbox)).</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mẫu thiết kế Decorator (Người trang trí) giúp mở rộng chức năng thay cho việc kế thừa như thế nào?</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1487,28 +1027,15 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Mẫu thiết kế Decorator (Người trang trí) giúp mở rộng chức năng thay cho việc kế thừa như thế nào?</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Kế thừa dẫn đến sự bùng nổ số lượng lớp (Class Explosion) khi cần kết hợp nhiều tính năng tùy chọn. Decorator giải quyết bằng cách 'bao bọc' (Wrap) đối tượng gốc bên trong một đối tượng Decorator có cùng interface với đối tượng gốc. Khi gọi hàm, Decorator thực thi hành vi bổ sung của nó trước hoặc sau khi ủy quyền cho đối tượng bên trong. Nhờ đó, ta có thể linh hoạt bổ sung chức năng cho đối tượng lúc Runtime một cách đệ quy (ví dụ: Cafe -&gt; MilkDecorator -&gt; SugarDecorator).</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mẫu thiết kế Adapter (Bộ chuyển đổi) giải quyết vấn đề gì giữa hai interface không tương thích?</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1520,25 +1047,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Mẫu thiết kế Adapter (Bộ chuyển đổi) giải quyết vấn đề gì giữa hai interface không tương thích?</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Adapter đóng vai trò cầu nối trung gian, bọc một lớp đang có (Adaptee - có interface cũ hoặc thư viện bên thứ 3) và chuyển đổi giao diện của nó thành giao diện mà Client mong đợi (Target Interface). Giống như bộ chuyển đổi giắc cắm điện chân tròn sang chân dẹt, Adapter giúp các lớp không tương thích về mặt giao diện có thể làm việc trơn tru với nhau mà không phải sửa mã nguồn gốc.</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nguyên lý Dependency Inversion Principle (DIP) trong SOLID phát biểu thế nào và liên hệ với Inversion of Control (IoC)?</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1548,29 +1062,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Nguyên lý Dependency Inversion Principle (DIP) trong SOLID phát biểu thế nào và liên hệ với Inversion of Control (IoC)?</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>- DIP: 1. Các module cấp cao không được phụ thuộc trực tiếp vào các module cấp thấp, cả hai phải cùng phụ thuộc vào Trừu tượng (Abstraction/Interface). 2. Trừu tượng không phụ thuộc vào chi tiết, chi tiết phải phụ thuộc vào trừu tượng.
-- IoC: Là kỹ thuật đảo ngược quyền điều khiển luồng chương trình; thay vì module cấp cao tự dùng từ khóa 'new' để tạo phụ thuộc cụ thể, các phụ thuộc này được 'tiêm' (Inject) từ bên ngoài vào thông qua Dependency Injection (Constructor Injection, Setter Injection).</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mẫu thiết kế Composite (Hợp thành) xử lý cấu trúc cây phân cấp như thế nào?</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1582,25 +1082,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Mẫu thiết kế Composite (Hợp thành) xử lý cấu trúc cây phân cấp như thế nào?</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Composite cho phép coi các đối tượng đơn lẻ (Leaf) và các nhóm tập hợp đối tượng (Composite) theo cùng một cách đồng nhất thông qua một interface chung Component. Ví dụ: Cấu trúc thư mục máy tính gồm File (Leaf) và Folder (Composite). Khi gọi hàm calculateSize(), Folder sẽ đệ quy gọi calculateSize() trên tất cả con của nó (kể cả file và folder con) mà Client không cần kiểm tra kiểu dữ liệu.</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mẫu thiết kế Command (Lệnh) biến một yêu cầu thành đối tượng để hỗ trợ tính năng Undo/Redo ra sao?</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1612,25 +1099,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Mẫu thiết kế Command (Lệnh) biến một yêu cầu thành đối tượng để hỗ trợ tính năng Undo/Redo ra sao?</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Command đóng gói toàn bộ thông tin của một yêu cầu thực thi (hành động, đối tượng Receiver thực hiện, các tham số) vào một đối tượng Command riêng biệt có hàm execute() và undo(). Hệ thống lưu trữ lịch sử các đối tượng Command này vào ngăn xếp (Stack). Khi người dùng bấm Undo, hệ thống chỉ việc pop lệnh gần nhất ra và gọi hàm undo() để hoàn tác lại trạng thái trước đó.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mẫu thiết kế Proxy (Ủy nhiệm) gồm những biến thể chính nào?</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1645,28 +1119,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Mẫu thiết kế Proxy (Ủy nhiệm) gồm những biến thể chính nào?</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1. Remote Proxy: Đại diện cho một đối tượng nằm ở không gian địa chỉ hoặc máy chủ khác (như RPC, gRPC stub).
-2. Virtual Proxy: Trì hoãn việc khởi tạo tốn kém tài nguyên của đối tượng cho đến khi thực sự cần dùng đến (Lazy Initialization, như tải ảnh dung lượng lớn trong văn bản).
-3. Protection Proxy: Kiểm tra quyền truy cập và bảo mật của người dùng trước khi cho phép gọi đối tượng thực sự.
-4. Logging/Caching Proxy: Tự động lưu log hoặc lưu cache kết quả trả về của các truy vấn đắt đỏ.</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mẫu thiết kế State (Trạng thái) giúp loại bỏ câu lệnh if-else phức tạp khi đối tượng chuyển trạng thái thế nào?</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1678,25 +1136,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Mẫu thiết kế State (Trạng thái) giúp loại bỏ câu lệnh if-else phức tạp khi đối tượng chuyển trạng thái thế nào?</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Thay vì dùng biến cờ trạng thái kèm chuỗi câu lệnh if-else hoặc switch-case khổng lồ, State Pattern đóng gói các hành vi tương ứng với từng trạng thái vào các lớp riêng biệt có chung interface State. Đối tượng Context nắm giữ con trỏ tới State hiện tại và ủy quyền thực thi hành vi cho nó. Khi chuyển trạng thái, Context chỉ cần thay đổi con trỏ trỏ sang đối tượng State mới.</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Phân biệt mẫu thiết kế Template Method và Strategy.</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1709,26 +1154,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Phân biệt mẫu thiết kế Template Method và Strategy.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>- Template Method: Dùng Kế thừa (Inheritance). Lớp cha định nghĩa khung sườn (skeleton) thuật toán trong một phương thức cố định (thường là final), các bước chi tiết được khai báo là hàm ảo trừu tượng để lớp con ghi đè cài đặt lại.
-- Strategy: Dùng Ủy quyền/Kết hợp (Composition). Đóng gói toàn bộ thuật toán vào một đối tượng riêng biệt có thể hoán đổi linh hoạt lúc Runtime thông qua Interface.</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Nguyên lý Open/Closed Principle (OCP) trong SOLID phát biểu như thế nào?</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1740,25 +1171,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Nguyên lý Open/Closed Principle (OCP) trong SOLID phát biểu như thế nào?</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Một thực thể phần mềm (lớp, module, hàm) phải 'Mở cho việc mở rộng (Open for extension), nhưng Đóng đối với việc sửa đổi (Closed for modification)'. Nghĩa là khi hệ thống có yêu cầu nghiệp vụ mới, ta phải bổ sung tính năng bằng cách viết thêm code mới (tạo thêm lớp con, kế thừa interface) chứ không được chỉnh sửa mã nguồn của các lớp đang hoạt động ổn định.</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Phân biệt tính tất định (DFA) và không tất định (NFA). Hai mô hình này có tương đương về sức mạnh đoán nhận không?</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1767,28 +1185,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Phân biệt tính tất định (DFA) và không tất định (NFA). Hai mô hình này có tương đương về sức mạnh đoán nhận không?</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Trong DFA, từ mỗi trạng thái khi đọc một ký tự đầu vào chỉ có DUY NHẤT một bước chuyển trạng thái xác định. Trong NFA, từ một trạng thái có thể có 0, 1 hoặc NHIỀU bước chuyển kế tiếp cho cùng một ký tự, và có thể có bước chuyển rỗng epsilon (không tốn ký tự). Hai mô hình này HOÀN TOÀN TƯƠNG ĐƯƠNG VỀ SỨC MẠNH ĐOÁN NHẬN: Mọi NFA đều có thể chuyển đổi thành một DFA tương đương bằng Thuật toán Xây dựng tập con (Subset Construction / Powerset Construction).</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mục đích chính của Bổ đề bơm (Pumping Lemma) cho Ngôn ngữ chính quy (Regular Language) là gì?</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1797,28 +1202,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Mục đích chính của Bổ đề bơm (Pumping Lemma) cho Ngôn ngữ chính quy (Regular Language) là gì?</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Bổ đề bơm KHÔNG DÙNG để chứng minh một ngôn ngữ là chính quy, mà dùng để CHỨNG MINH MỘT NGÔN NGỮ KHÔNG PHẢI LÀ CHÍNH QUY bằng phương pháp phản chứng. Bổ đề phát biểu: Nếu L là chính quy, tồn tại hằng số bơm p sao cho mọi chuỗi w thuộc L có độ dài &gt;= p đều tách được thành w = xyz với |xy| &lt;= p, |y| &gt; 0 và x(y^i)z thuộc L với mọi i &gt;= 0. Nếu ta chỉ ra được một giá trị i làm x(y^i)z không thuộc L, ta kết luận L không chính quy (ví dụ ngôn ngữ a^n b^n).</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Văn phạm phi ngữ cảnh (Context-Free Grammar - CFG) ở Dạng chuẩn Chomsky (CNF) có cấu trúc các luật sinh thế nào?</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1830,31 +1222,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Văn phạm phi ngữ cảnh (Context-Free Grammar - CFG) ở Dạng chuẩn Chomsky (CNF) có cấu trúc các luật sinh thế nào?</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Mọi luật sinh trong Dạng chuẩn Chomsky (CNF) chỉ được phép có một trong hai dạng sau:
-1. A -&gt; BC (Vế phải gồm đúng hai biến không kết thúc B, C, trong đó B và C không phải là biến bắt đầu S nếu ngôn ngữ chứa chuỗi rỗng).
-2. A -&gt; a (Vế phải gồm đúng một ký tự kết thúc a).
-Dạng chuẩn CNF là điều kiện tiên quyết để chạy thuật toán phân tích cú pháp CYK (Cocke-Younger-Kasami) trong thời gian đa thức O(n^3).</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Khái niệm Tính nhập nhằng (Ambiguity) trong Văn phạm phi ngữ cảnh (CFG).</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1866,25 +1242,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Khái niệm Tính nhập nhằng (Ambiguity) trong Văn phạm phi ngữ cảnh (CFG).</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Một văn phạm CFG được gọi là Nhập nhằng (Ambiguous) nếu tồn tại ít nhất một chuỗi ký tự trong ngôn ngữ có từ HAI CÂY DẪN XUẤT CÚ PHÁP (Parse Trees) KHÁC NHAU (hoặc tương đương: có từ hai dẫn xuất trái nhất/phải nhất khác nhau). Nhập nhằng là điều tối kỵ trong thiết kế ngôn ngữ lập trình vì nó làm cho một câu lệnh có thể được hiểu theo nhiều ngữ nghĩa khác nhau (ví dụ: biểu thức 2 + 3 * 4).</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Automata đẩy xuống (Pushdown Automata - PDA) mở rộng từ NFA bằng cách bổ sung thành phần nào?</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1896,25 +1259,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Automata đẩy xuống (Pushdown Automata - PDA) mở rộng từ NFA bằng cách bổ sung thành phần nào?</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>PDA mở rộng từ NFA bằng cách gắn thêm một Ngăn xếp (Stack) có sức chứa vô hạn. Nhờ có ngăn xếp để ghi nhớ số lượng ký tự (bằng thao tác Push và Pop), PDA có khả năng đoán nhận lớp Ngôn ngữ phi ngữ cảnh (Context-Free Languages), ví dụ đoán nhận được ngôn ngữ cân bằng ngoặc hoặc ngôn ngữ L = {w w^R | w in {0, 1}*}, điều mà DFA/NFA bất lực.</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bài toán Dừng (Halting Problem) của Máy Turing phát biểu thế nào và ý nghĩa của nó?</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1926,25 +1276,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Bài toán Dừng (Halting Problem) của Máy Turing phát biểu thế nào và ý nghĩa của nó?</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Bài toán Dừng do Alan Turing chứng minh năm 1936: Bất khả thi để xây dựng một thuật toán tổng quát có thể nhận đầu vào là một chương trình máy tính tùy ý và đầu vào của nó, rồi xác định chính xác chương trình đó cuối cùng sẽ Dừng lại hay chạy Vô tận. Ý nghĩa: Nó chứng minh rằng tồn tại những giới hạn tuyệt đối của điện toán; có những bài toán toán học mà máy tính vĩnh viễn không thể giải tự động được (Undecidable Problems).</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Phân cấp Chomsky (Chomsky Hierarchy) phân chia các lớp ngôn ngữ hình thức thành 4 cấp nào?</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1960,29 +1297,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Phân cấp Chomsky (Chomsky Hierarchy) phân chia các lớp ngôn ngữ hình thức thành 4 cấp nào?</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Theo thứ tự bao hàm từ hẹp đến rộng:
-- Loại 3: Ngôn ngữ chính quy (Regular Languages) - đoán nhận bởi DFA / NFA / Biểu thức chính quy.
-- Loại 2: Ngôn ngữ phi ngữ cảnh (Context-Free Languages) - đoán nhận bởi Pushdown Automata (PDA).
-- Loại 1: Ngôn ngữ cảm ngữ cảnh (Context-Sensitive Languages) - đoán nhận bởi Linear Bounded Automata (LBA).
-- Loại 0: Ngôn ngữ đệ quy liệt kê được (Recursively Enumerable Languages) - đoán nhận bởi Máy Turing (Turing Machine).</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Thuật toán Cực tiểu hóa trạng thái DFA (Table-Filling Algorithm) hoạt động dựa trên nguyên lý nào?</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1994,25 +1314,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Thuật toán Cực tiểu hóa trạng thái DFA (Table-Filling Algorithm) hoạt động dựa trên nguyên lý nào?</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Thuật toán dựa trên quan hệ tương đương tương thích giữa các trạng thái (Myhill-Nerode Theorem). Hai trạng thái p và q được coi là phân biệt được (distinguishable) nếu tồn tại một chuỗi w sao cho khi đọc w, một trạng thái chuyển vào tập trạng thái kết thúc F còn trạng thái kia chuyển vào trạng thái không kết thúc. Thuật toán lập bảng tam giác, đánh dấu các cặp phân biệt được; các cặp không bị đánh dấu sau khi duyệt hết sẽ được gộp lại thành một trạng thái duy nhất.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sự khác biệt giữa Máy Turing tất định (DTM) và Máy Turing không tất định (NTM).</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2024,25 +1331,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Sự khác biệt giữa Máy Turing tất định (DTM) và Máy Turing không tất định (NTM).</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Trong DTM, với mỗi trạng thái và ký tự đọc được trên băng, hàm chuyển trạng thái xác định duy nhất 1 bộ (trạng thái mới, ký tự ghi đè, hướng dịch chuyển L/R). Trong NTM, hàm chuyển trạng thái có thể cho phép nhiều lựa chọn kế tiếp. Mặc dù NTM có thể tìm đường đi nhanh hơn theo lý thuyết độ phức tạp (lớp NP), DTM và NTM HOÀN TOÀN TƯƠNG ĐƯƠNG VỀ MẶT NĂNG LỰC TÍNH TOÁN: Mọi bài toán giải được bằng NTM đều giải được bằng DTM.</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Giải thuật chuyển đổi từ Biểu thức chính quy (Regex) sang epsilon-NFA (Thuật toán Thompson).</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2054,109 +1348,55 @@
           <t>no</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Giải thuật chuyển đổi từ Biểu thức chính quy (Regex) sang epsilon-NFA (Thuật toán Thompson).</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Thuật toán Thompson xây dựng epsilon-NFA bằng phương pháp đệ quy cấu trúc: Tạo các khối automata cơ sở cho ký tự rỗng epsilon và ký tự đơn a. Sau đó dùng các quy tắc ghép nối cho 3 phép toán chính quy: 1. Phép nối (Concatenation: nối trạng thái kết thúc của A với trạng thái bắt đầu của B). 2. Phép hợp (Union: dùng trạng thái bắt đầu mới rẽ 2 nhánh epsilon sang A và B). 3. Bao đóng Kleene (Star: thêm vòng lặp epsilon từ kết thúc về bắt đầu).</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>HCMUS FIT Academic Syllabus</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Bạn có biết các Agent khác trong hệ sinh thái HCMUS Smart Campus không?</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HeThong_Agent</t>
+          <t>Tôi là Trợ giảng Chuyên ngành (Specialized Major Tutor Agent) thuộc tầng 4 cao nhất trong Sub-space 4. Tôi phối hợp cùng Core Foundations Tutor Agent (Cơ sở ngành), General Education Tutor Agent (Đại cương), Political Theory Tutor Agent (Chính trị), Library Research Agent (Tra cứu bài báo nghiên cứu) và Campus Router Agent.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NhanDienHeThong</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Bạn có biết các Agent khác trong hệ sinh thái HCMUS Smart Campus không?</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Tôi là Trợ giảng Chuyên ngành (Specialized Major Tutor Agent) thuộc tầng 4 cao nhất trong Sub-space 4. Tôi phối hợp cùng Core Foundations Tutor Agent (Cơ sở ngành), General Education Tutor Agent (Đại cương), Political Theory Tutor Agent (Chính trị), Library Research Agent (Tra cứu bài báo nghiên cứu) và Campus Router Agent.</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>HCMUS Smart Campus Directory &amp; Relationship Graph</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Môn Xử lý ngôn ngữ tự nhiên (CSC15006) học những nội dung gì?</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HeThong_Agent</t>
+          <t>Môn NLP CSC15006 cung cấp nền tảng từ tiền xử lý văn bản, mô hình ngôn ngữ thống kê, Word2Vec, GloVe, đến kiến trúc Seq2Seq và Transformers (BERT, GPT). Sinh viên thực hiện đồ án phân tích cảm xúc, tóm tắt văn bản, dịch máy hoặc xây dựng chatbot.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NhanDienHeThong</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Môn Xử lý ngôn ngữ tự nhiên (CSC15006) học những nội dung gì?</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Môn NLP CSC15006 cung cấp nền tảng từ tiền xử lý văn bản, mô hình ngôn ngữ thống kê, Word2Vec, GloVe, đến kiến trúc Seq2Seq và Transformers (BERT, GPT). Sinh viên thực hiện đồ án phân tích cảm xúc, tóm tắt văn bản, dịch máy hoặc xây dựng chatbot.</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>HCMUS Smart Campus Directory &amp; Relationship Graph</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Điều kiện và quy trình làm Khóa luận tốt nghiệp (KLTN) Khoa CNTT như thế nào?</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HeThong_Agent</t>
+          <t>Sinh viên cần đạt CPA tích lũy &gt;= 7.0 (thang 10), hoàn thành đủ số tín chỉ quy định và không nợ môn học phần bắt buộc. Quy trình gồm: Chọn đề tài và GVHD, bảo vệ đề cương, nghiên cứu thực nghiệm 4-5 tháng, viết báo cáo luận văn, kiểm tra đạo văn Turnitin (&lt; 20%) và bảo vệ trước Hội đồng chấm điểm tốt nghiệp.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NhanDienHeThong</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Điều kiện và quy trình làm Khóa luận tốt nghiệp (KLTN) Khoa CNTT như thế nào?</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Sinh viên cần đạt CPA tích lũy &gt;= 7.0 (thang 10), hoàn thành đủ số tín chỉ quy định và không nợ môn học phần bắt buộc. Quy trình gồm: Chọn đề tài và GVHD, bảo vệ đề cương, nghiên cứu thực nghiệm 4-5 tháng, viết báo cáo luận văn, kiểm tra đạo văn Turnitin (&lt; 20%) và bảo vệ trước Hội đồng chấm điểm tốt nghiệp.</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>HCMUS Smart Campus Directory &amp; Relationship Graph</t>
+          <t>no</t>
         </is>
       </c>
     </row>
